--- a/02_加值成品/八下/八下1-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-4 化學反應的能量　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下1-4 化學反應的能量　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>放出熱量使周圍變熱的反應是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>放熱反應</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>熱與光</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>升溫</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>吸收熱量使周圍變冷的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>吸熱反應</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>降溫</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>燃燒是放熱還吸熱？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>發熱</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>光合作用是放熱還吸熱？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>吸熱</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>熱與光</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>周圍環境</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>放熱反應</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>吸光能</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>暖暖包利用哪種反應？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>吸熱反應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>放熱反應</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>發熱</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>化學反應中能量會？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>熱與光</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>吸熱反應</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>中和反應通常是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>熱與光</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>升溫</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>冷敷包利用哪種反應？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>吸熱反應</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>降溫</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>放熱反應使周圍溫度？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>放熱</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>吸熱反應使周圍溫度？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>熱與光</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>下降</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>吸熱</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-4 化學反應的能量　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下1-4 化學反應的能量　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>放熱反應使溫度計讀數？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>吸熱反應使溫度計讀數？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>下降</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>吸熱</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>食物提供人體什麼能？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>熱與光</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>化學能</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>營養</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>反應放光放熱屬於？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>放熱反應</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>吸熱反應</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>燃燒</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>某鹽溶於水杯變冷是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>放熱</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>熱與光</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>吸熱</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>溶解吸熱</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>化學能可轉成哪些能？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>吸熱反應</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>熱光電</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>多形式</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>生鏽緩慢放熱屬於？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>放熱反應</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>吸熱反應</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>氧化</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>植物把光能轉成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>吸熱反應</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>化學能</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>熱光電</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>變冷</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>光合</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>燃燒放出的能量形式主要是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>吸熱反應</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>熱與光</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>某反應使溫度計下降屬？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>熱光電</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>變冷</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>吸熱反應</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>吸熱</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-4 化學反應的能量　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下1-4 化學反應的能量　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何用溫度計判別放吸熱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>反應後升溫為放熱、降溫為吸熱</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>需啟動能越過能障</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>測反應前後溫度變化</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>化學能與熱光等互換總量不變</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>暖暖包鐵粉氧化屬何反應?為何發熱？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>放熱氧化反應釋出熱能</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>測反應前後溫度變化</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>反應中鍵能變化釋放或吸收能量</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>化學能與熱光等互換總量不變</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>放熱反應為何有些仍要點火？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>測反應前後溫度變化</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>需啟動能越過能障</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>燃燒放熱、光合吸能</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>反應中鍵能變化釋放或吸收能量</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>活化能</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>能量守恆在化學反應如何體現？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>燃燒放熱、光合吸能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>化學能與熱光等互換總量不變</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>反應中鍵能變化釋放或吸收能量</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>反應後升溫為放熱、降溫為吸熱</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>冷敷包溶解吸熱使周圍？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>放熱反應</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>變冷</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>降溫</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>燃料電池把化學能轉成？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>熱與光</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>守恆</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>放熱反應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>比較燃燒與光合的能量方向？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>放熱氧化反應釋出熱能</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>測反應前後溫度變化</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>反應中鍵能變化釋放或吸收能量</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>燃燒放熱、光合吸能</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>相反</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>反應吸熱時能量來自？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>電能</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>周圍環境</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>吸收</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>如何實驗判斷反應放熱或吸熱？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>放熱氧化反應釋出熱能</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>測反應前後溫度變化</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>化學能與熱光等互換總量不變</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>反應後升溫為放熱、降溫為吸熱</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何化學能可轉為其他形式能量？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>燃燒放熱、光合吸能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>需啟動能越過能障</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>化學能與熱光等互換總量不變</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>反應中鍵能變化釋放或吸收能量</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>轉換</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下1-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>升溫</t>
+          <t>升溫：這種反應會把熱能釋放到周圍環境中，所以摸起來或量起來溫度會上升</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>降溫</t>
+          <t>降溫：這種反應會把周圍的熱能吸收進去，所以周圍環境的溫度反而會下降</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>發熱</t>
+          <t>發熱：物質燃燒時會釋放大量熱能，讓我們感覺到火焰旁邊很燙，是典型的放熱反應</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>吸光能</t>
+          <t>吸光能：植物行光合作用時需要吸收太陽的光能，才能把二氧化碳和水轉變成養分，屬於吸熱反應</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>發熱</t>
+          <t>發熱：暖暖包裡的鐵粉和氧氣反應會釋放熱量，所以搖一搖就會慢慢變熱</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：反應前後能量的總量不會改變，只是從一種形式（如化學能）轉換成另一種形式（如熱能）</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>升溫</t>
+          <t>升溫：酸和鹼混合反應時通常會釋放熱量，讓溶液溫度稍微上升</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>降溫</t>
+          <t>降溫：冷敷包裡的物質溶解或反應時會吸收周圍的熱，所以摸起來會感覺變冷</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：放熱反應會把反應中釋放出來的能量以熱的形式傳給周圍環境，使周圍溫度上升</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>吸熱：吸熱反應需要從周圍環境吸收能量才能進行，會使周圍環境失去熱量，溫度因此下降</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：因為反應把熱能釋放到周圍，插在裡面的溫度計就會測到溫度升高</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>吸熱：因為反應把周圍的熱能吸收走了，插在裡面的溫度計就會測到溫度降低</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>營養</t>
+          <t>營養：食物中的營養素含有化學能，人體消化後把這些能量釋放出來供身體使用</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>燃燒</t>
+          <t>燃燒：像燃燒這種同時發光又發熱的反應，代表它正在把化學能大量釋放到周圍</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>溶解吸熱</t>
+          <t>溶解吸熱：這種鹽溶解時需要吸收熱能才能溶解，所以會讓水杯周圍變得比較冷</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>多形式</t>
+          <t>多形式：物質裡儲存的化學能經過反應後，可以變成熱能、光能或電能等不同形式</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>氧化</t>
+          <t>氧化：鐵和氧氣緩慢反應生鏽的過程也會釋放熱量，只是速度慢到不容易察覺</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>光合</t>
+          <t>光合：植物利用光合作用，把太陽的光能轉變儲存成養分裡的化學能</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：燃燒是劇烈的氧化反應，會快速釋放出大量能量，主要以熱能和光能的形式表現出來</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>吸熱：反應進行時如果從周圍吸收熱量，會使周圍溫度下降，用溫度計測量就會看到讀數降低，這代表是吸熱反應</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：把溫度計放進反應容器裡，反應後溫度比原本高就是放熱，比原本低就是吸熱</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：鐵粉和空氣中的氧氣結合是氧化反應，這個過程會釋放出熱能，所以暖暖包會發熱</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>活化能</t>
+          <t>活化能：即使反應整體會放熱，一開始還是需要一點能量把反應「推」過起始的門檻才會開始進行</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：反應前物質中的化學能，轉換成熱能、光能等之後，加總起來的能量還是一樣多</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>降溫</t>
+          <t>降溫：冷敷包裡的物質溶解時把周圍的熱能吸收走，所以敷在皮膚上會感覺涼涼的</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：燃料電池利用化學反應把燃料中的化學能直接轉換成可以使用的電能</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>相反：燃燒是把化學能釋放出來變成熱和光，光合作用則是把光能吸收進去變成化學能，方向剛好相反</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>吸收</t>
+          <t>吸收：吸熱反應需要的能量並非自己產生，而是從反應容器周圍的環境中吸收過來的</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：可以用溫度計測量反應前後溶液或環境的溫度變化，溫度上升代表放熱反應，溫度下降代表吸熱反應</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>轉換：化學反應時舊的化學鍵斷裂、新的化學鍵形成，鍵結中儲存的能量會因此改變，這些能量差就會以熱、光等形式釋放或吸收，轉換成其他形式的能量</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下1-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-4_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>熱與光</t>
+          <t>守恆</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>周圍環境</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>上升</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>化學能</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>化學能</t>
+          <t>放熱</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>變冷</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>周圍環境</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>化學能</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>熱光電</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>化學能</t>
+          <t>熱與光</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>周圍環境</t>
+          <t>化學能</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>放熱反應</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>吸熱反應</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>吸熱反應</t>
+          <t>下降</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>熱與光</t>
+          <t>吸熱反應</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>熱光電</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>下降</t>
+          <t>守恆</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>化學能</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>上升</t>
+          <t>電能</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>吸熱</t>
+          <t>放熱</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>化學能</t>
+          <t>變冷</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>吸熱反應</t>
+          <t>守恆</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>變冷</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>吸熱</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>放熱</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>熱與光</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>吸熱</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>上升</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>吸熱反應</t>
+          <t>熱光電</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>吸熱</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>變冷</t>
+          <t>周圍環境</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
